--- a/rockphypy-main/data/Jorlin/sensitivity_summary.xlsx
+++ b/rockphypy-main/data/Jorlin/sensitivity_summary.xlsx
@@ -527,25 +527,25 @@
         <v>0.75</v>
       </c>
       <c r="D2" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E2" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F2" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G2" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H2" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I2" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -579,25 +579,25 @@
         <v>0.75</v>
       </c>
       <c r="D3" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E3" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F3" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G3" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H3" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I3" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -631,25 +631,25 @@
         <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E4" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F4" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G4" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H4" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I4" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -683,25 +683,25 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E5" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F5" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G5" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H5" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I5" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -735,25 +735,25 @@
         <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E6" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F6" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G6" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H6" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I6" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -784,28 +784,28 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E7" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F7" t="n">
-        <v>292.2488378604758</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G7" t="n">
-        <v>204.1212080144699</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H7" t="n">
-        <v>-42.71733391649285</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I7" t="n">
-        <v>-114.2622166240596</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5914291078657344</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5130613011236763</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="8">
@@ -836,46 +836,46 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E8" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F8" t="n">
-        <v>293.0985075382</v>
+        <v>374.0950646410671</v>
       </c>
       <c r="G8" t="n">
-        <v>199.595107021608</v>
+        <v>311.7599965019389</v>
       </c>
       <c r="H8" t="n">
-        <v>6.874168604799819</v>
+        <v>89.60131466339162</v>
       </c>
       <c r="I8" t="n">
-        <v>-106.1869554804285</v>
+        <v>-153.9340513545683</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05831178945753763</v>
+        <v>0.3559496880577213</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5225333570903435</v>
+        <v>0.5363685204163913</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.449264157340198</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5405563712720746</v>
+        <v>0.5408378903615838</v>
       </c>
       <c r="P8" t="n">
-        <v>0.243178094909691</v>
+        <v>0.3963912092357153</v>
       </c>
     </row>
     <row r="9">
@@ -888,46 +888,46 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E9" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F9" t="n">
-        <v>299.2924244128627</v>
+        <v>391.2895826486204</v>
       </c>
       <c r="G9" t="n">
-        <v>196.6836973369378</v>
+        <v>308.9975732020745</v>
       </c>
       <c r="H9" t="n">
-        <v>41.55790026567694</v>
+        <v>129.0237856701079</v>
       </c>
       <c r="I9" t="n">
-        <v>-100.7004929914529</v>
+        <v>-148.5758416682227</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4833927193551691</v>
+        <v>0.6985993598883644</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2154034431828822</v>
+        <v>0.2252314584059974</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5722979065957432</v>
+        <v>0.7642203876755415</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2284029696693686</v>
+        <v>0.2286024558818834</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3140418859058878</v>
+        <v>0.4057834971637355</v>
       </c>
     </row>
     <row r="10">
@@ -940,28 +940,28 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E10" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F10" t="n">
-        <v>306.8199852327052</v>
+        <v>406.4141812107608</v>
       </c>
       <c r="G10" t="n">
-        <v>194.641800269292</v>
+        <v>306.9978608420524</v>
       </c>
       <c r="H10" t="n">
-        <v>67.4784994282163</v>
+        <v>158.5358703205341</v>
       </c>
       <c r="I10" t="n">
-        <v>-96.68604266341661</v>
+        <v>-144.6528407587653</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -995,28 +995,28 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E11" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F11" t="n">
-        <v>297.6044614187397</v>
+        <v>350.3514079418571</v>
       </c>
       <c r="G11" t="n">
-        <v>249.3869608345065</v>
+        <v>358.7397100831212</v>
       </c>
       <c r="H11" t="n">
-        <v>-64.88833483477902</v>
+        <v>-32.93659146218013</v>
       </c>
       <c r="I11" t="n">
-        <v>-188.2809363726923</v>
+        <v>-243.2543514124797</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2495467474959456</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1025,13 +1025,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7139864943046353</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6018685698995038</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="12">
@@ -1047,43 +1047,43 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E12" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F12" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G12" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H12" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I12" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.2207182154215445</v>
       </c>
       <c r="L12" t="n">
-        <v>0.292012081752508</v>
+        <v>0.3894264795153263</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.005715558035035775</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5265120878154822</v>
+        <v>0.5253245493892168</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1586480359029283</v>
+        <v>0.2501899281854278</v>
       </c>
     </row>
     <row r="13">
@@ -1099,43 +1099,43 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E13" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F13" t="n">
-        <v>300.6429645904989</v>
+        <v>366.4978643604688</v>
       </c>
       <c r="G13" t="n">
-        <v>181.8460720157691</v>
+        <v>296.8355856852156</v>
       </c>
       <c r="H13" t="n">
-        <v>53.98654769455164</v>
+        <v>76.86073405865727</v>
       </c>
       <c r="I13" t="n">
-        <v>-53.05764474383204</v>
+        <v>-109.3090828419182</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4178237880230007</v>
+        <v>0.6059130638329222</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0396394267414077</v>
+        <v>0.1181977214019563</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5798170441905008</v>
+        <v>0.5822350006911727</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2200817485499617</v>
+        <v>0.2193028546617311</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2449750317527542</v>
+        <v>0.3213942036889516</v>
       </c>
     </row>
     <row r="14">
@@ -1151,25 +1151,25 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E14" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F14" t="n">
-        <v>311.1550597704142</v>
+        <v>376.999548380473</v>
       </c>
       <c r="G14" t="n">
-        <v>179.0582835653377</v>
+        <v>288.5378905818998</v>
       </c>
       <c r="H14" t="n">
-        <v>88.12803922105043</v>
+        <v>108.3771653616102</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.89957059820165</v>
+        <v>-71.68299449080907</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -1200,31 +1200,31 @@
         <v>0.15</v>
       </c>
       <c r="C15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D15" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E15" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F15" t="n">
-        <v>360.0466693094172</v>
+        <v>375.3123240708977</v>
       </c>
       <c r="G15" t="n">
-        <v>176.0216217761862</v>
+        <v>255.6250837336162</v>
       </c>
       <c r="H15" t="n">
-        <v>223.8060310319925</v>
+        <v>156.8627780229932</v>
       </c>
       <c r="I15" t="n">
-        <v>83.20460779280856</v>
+        <v>-36.98381447245407</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2787572020414447</v>
+        <v>0.0135650336873643</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5074525555301388</v>
+        <v>0.1946919093204228</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1521381370875755</v>
+        <v>0.03168885381359306</v>
       </c>
     </row>
     <row r="16">
@@ -1252,34 +1252,34 @@
         <v>0.25</v>
       </c>
       <c r="C16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D16" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E16" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F16" t="n">
-        <v>293.0985075382</v>
+        <v>372.0503779934263</v>
       </c>
       <c r="G16" t="n">
-        <v>199.595107021608</v>
+        <v>401.2575169234997</v>
       </c>
       <c r="H16" t="n">
-        <v>6.874168604799819</v>
+        <v>-76.02340726139353</v>
       </c>
       <c r="I16" t="n">
-        <v>-106.1869554804285</v>
+        <v>-281.07601049064</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0528511087280152</v>
+        <v>0.2235939461298668</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1288,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04542173664502831</v>
+        <v>0.301289516800072</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02158913630015125</v>
+        <v>0.1069253441514008</v>
       </c>
     </row>
     <row r="17">
@@ -1304,46 +1304,46 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D17" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E17" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F17" t="n">
-        <v>345.7645966398385</v>
+        <v>450.2403436682577</v>
       </c>
       <c r="G17" t="n">
-        <v>334.9977221280125</v>
+        <v>584.0484136752251</v>
       </c>
       <c r="H17" t="n">
-        <v>-169.8063859625917</v>
+        <v>-253.6356650886484</v>
       </c>
       <c r="I17" t="n">
-        <v>-281.4272648557501</v>
+        <v>-496.577472746785</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2192898393626984</v>
+        <v>0.3251585075910084</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3564200659078181</v>
+        <v>0.5042384222682663</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3811352060103801</v>
+        <v>0.4277577777921734</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3917622972452341</v>
+        <v>0.5672887273116012</v>
       </c>
       <c r="P17" t="n">
-        <v>0.274902473399521</v>
+        <v>0.3791200521174748</v>
       </c>
     </row>
     <row r="18">
@@ -1356,46 +1356,46 @@
         <v>0.45</v>
       </c>
       <c r="C18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D18" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E18" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F18" t="n">
-        <v>439.5490500181634</v>
+        <v>537.5522551295661</v>
       </c>
       <c r="G18" t="n">
-        <v>482.2657380227039</v>
+        <v>755.1745646985914</v>
       </c>
       <c r="H18" t="n">
-        <v>-315.0309788813299</v>
+        <v>-388.5191303242152</v>
       </c>
       <c r="I18" t="n">
-        <v>-442.3732689517539</v>
+        <v>-684.2133559890809</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6097873694975402</v>
+        <v>0.6882512725084871</v>
       </c>
       <c r="L18" t="n">
-        <v>0.686590926906023</v>
+        <v>0.7669736561391509</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7208482844760732</v>
+        <v>0.7526083937118827</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7098519507255135</v>
+        <v>0.7988927094078337</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5747795468583876</v>
+        <v>0.6374215657735702</v>
       </c>
     </row>
     <row r="19">
@@ -1408,28 +1408,28 @@
         <v>0.55</v>
       </c>
       <c r="C19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D19" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E19" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F19" t="n">
-        <v>533.2650800282755</v>
+        <v>612.5176081271693</v>
       </c>
       <c r="G19" t="n">
-        <v>622.0573968577797</v>
+        <v>906.9505588218279</v>
       </c>
       <c r="H19" t="n">
-        <v>-434.3660790565318</v>
+        <v>-491.2403058154811</v>
       </c>
       <c r="I19" t="n">
-        <v>-589.181467885751</v>
+        <v>-847.1420921670586</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1460,31 +1460,31 @@
         <v>0.005</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D20" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E20" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F20" t="n">
-        <v>825.8924565306975</v>
+        <v>498.8078606575803</v>
       </c>
       <c r="G20" t="n">
-        <v>1142.504311688031</v>
+        <v>680.4702797183257</v>
       </c>
       <c r="H20" t="n">
-        <v>-766.9016605469527</v>
+        <v>-330.0832267480137</v>
       </c>
       <c r="I20" t="n">
-        <v>-1124.758884951912</v>
+        <v>-601.8273329114716</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.5900558987338288</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -1493,13 +1493,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0.6096951378098884</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6842581336110779</v>
       </c>
     </row>
     <row r="21">
@@ -1512,46 +1512,46 @@
         <v>0.01</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D21" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E21" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F21" t="n">
-        <v>510.9146926707245</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G21" t="n">
-        <v>587.5578967994219</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H21" t="n">
-        <v>-407.150008313764</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I21" t="n">
-        <v>-553.5693433766803</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4088188042383186</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4114529669005246</v>
+        <v>0.1328225757097569</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5266596852781082</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4392251297641686</v>
+        <v>0.08624846266816583</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3723469081885661</v>
+        <v>0.05027051629823996</v>
       </c>
     </row>
     <row r="22">
@@ -1564,31 +1564,31 @@
         <v>0.02</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D22" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E22" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F22" t="n">
-        <v>293.0985075382</v>
+        <v>457.4514059189218</v>
       </c>
       <c r="G22" t="n">
-        <v>199.595107021608</v>
+        <v>260.0327412170168</v>
       </c>
       <c r="H22" t="n">
-        <v>6.874168604799819</v>
+        <v>326.5729432979623</v>
       </c>
       <c r="I22" t="n">
-        <v>-106.1869554804285</v>
+        <v>120.2810102179581</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.4188991915365259</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1597,13 +1597,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.6024821573277034</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.2057543629143936</v>
       </c>
     </row>
     <row r="23">
@@ -1616,46 +1616,46 @@
         <v>0.04</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D23" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E23" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F23" t="n">
-        <v>431.4406503308625</v>
+        <v>597.8623175176947</v>
       </c>
       <c r="G23" t="n">
-        <v>224.8254492057673</v>
+        <v>347.2891781067157</v>
       </c>
       <c r="H23" t="n">
-        <v>331.3216493598058</v>
+        <v>520.0297684868171</v>
       </c>
       <c r="I23" t="n">
-        <v>168.0719761610279</v>
+        <v>278.382039861792</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2596541177959411</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02675797633461973</v>
+        <v>0.2075372175394543</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4268891378204254</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.06075665241698771</v>
+        <v>0.3283194621017995</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1514957112140764</v>
+        <v>0.5347705567401012</v>
       </c>
     </row>
     <row r="24">
@@ -1668,31 +1668,31 @@
         <v>0.1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D24" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E24" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F24" t="n">
-        <v>315.3637644556865</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G24" t="n">
-        <v>276.3869798361439</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H24" t="n">
-        <v>-101.4047373154019</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I24" t="n">
-        <v>-211.8653031785392</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -1701,13 +1701,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="25">
@@ -1720,46 +1720,46 @@
         <v>0.15</v>
       </c>
       <c r="C25" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D25" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E25" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F25" t="n">
-        <v>293.0985075382</v>
+        <v>362.8792290807827</v>
       </c>
       <c r="G25" t="n">
-        <v>199.595107021608</v>
+        <v>274.605777555574</v>
       </c>
       <c r="H25" t="n">
-        <v>6.874168604799819</v>
+        <v>106.2205030539993</v>
       </c>
       <c r="I25" t="n">
-        <v>-106.1869554804285</v>
+        <v>-86.77059734005977</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.2974599464438025</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3200667269648373</v>
+        <v>0.3423357467115819</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.5473285844483773</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4457925563881248</v>
+        <v>0.4423655444330253</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1551322871882571</v>
+        <v>0.324183645027453</v>
       </c>
     </row>
     <row r="26">
@@ -1772,46 +1772,46 @@
         <v>0.2</v>
       </c>
       <c r="C26" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D26" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E26" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F26" t="n">
-        <v>296.9540467485266</v>
+        <v>371.6838381549516</v>
       </c>
       <c r="G26" t="n">
-        <v>172.8644956390651</v>
+        <v>259.6756055729457</v>
       </c>
       <c r="H26" t="n">
-        <v>64.46875374872677</v>
+        <v>143.9558683721002</v>
       </c>
       <c r="I26" t="n">
-        <v>-52.70259165588148</v>
+        <v>-49.23681935325237</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1731639219172273</v>
+        <v>0.6915289547780052</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08338761729578596</v>
+        <v>0.1044169905498435</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6092694239494979</v>
+        <v>0.830827158122505</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1653052740444817</v>
+        <v>0.1634572400735049</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1839539680600009</v>
+        <v>0.3694537555502438</v>
       </c>
     </row>
     <row r="27">
@@ -1824,31 +1824,31 @@
         <v>0.25</v>
       </c>
       <c r="C27" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D27" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E27" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F27" t="n">
-        <v>304.5837387089292</v>
+        <v>378.575948182484</v>
       </c>
       <c r="G27" t="n">
-        <v>163.4466725148921</v>
+        <v>253.1231014662167</v>
       </c>
       <c r="H27" t="n">
-        <v>99.31904059632528</v>
+        <v>166.4737911517984</v>
       </c>
       <c r="I27" t="n">
-        <v>-21.18156387438111</v>
+        <v>-27.23974123345996</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5158364537760635</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1857,13 +1857,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.9779362723875934</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.2870870257056743</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
   </sheetData>
@@ -1975,43 +1975,43 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E2" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F2" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G2" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H2" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I2" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.2207182154215445</v>
       </c>
       <c r="L2" t="n">
-        <v>0.292012081752508</v>
+        <v>0.3894264795153263</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.005715558035035775</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5265120878154822</v>
+        <v>0.5253245493892168</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1586480359029283</v>
+        <v>0.2501899281854278</v>
       </c>
     </row>
     <row r="3">
@@ -2024,46 +2024,46 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E3" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F3" t="n">
-        <v>293.0985075382</v>
+        <v>374.0950646410671</v>
       </c>
       <c r="G3" t="n">
-        <v>199.595107021608</v>
+        <v>311.7599965019389</v>
       </c>
       <c r="H3" t="n">
-        <v>6.874168604799819</v>
+        <v>89.60131466339162</v>
       </c>
       <c r="I3" t="n">
-        <v>-106.1869554804285</v>
+        <v>-153.9340513545683</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05831178945753763</v>
+        <v>0.3559496880577213</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5225333570903435</v>
+        <v>0.5363685204163913</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.449264157340198</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5405563712720746</v>
+        <v>0.5408378903615838</v>
       </c>
       <c r="P3" t="n">
-        <v>0.243178094909691</v>
+        <v>0.3963912092357153</v>
       </c>
     </row>
     <row r="4">
@@ -2079,25 +2079,25 @@
         <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E4" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F4" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G4" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H4" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I4" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -2128,46 +2128,46 @@
         <v>0.15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E5" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F5" t="n">
-        <v>293.0985075382</v>
+        <v>362.8792290807827</v>
       </c>
       <c r="G5" t="n">
-        <v>199.595107021608</v>
+        <v>274.605777555574</v>
       </c>
       <c r="H5" t="n">
-        <v>6.874168604799819</v>
+        <v>106.2205030539993</v>
       </c>
       <c r="I5" t="n">
-        <v>-106.1869554804285</v>
+        <v>-86.77059734005977</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.2974599464438025</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3200667269648373</v>
+        <v>0.3423357467115819</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5473285844483773</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4457925563881248</v>
+        <v>0.4423655444330253</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1551322871882571</v>
+        <v>0.324183645027453</v>
       </c>
     </row>
     <row r="6">
@@ -2177,37 +2177,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D6" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E6" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F6" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="G6" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="H6" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="I6" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1328225757097569</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.08624846266816583</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.05027051629823996</v>
       </c>
     </row>
     <row r="7">
@@ -2229,49 +2229,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="E7" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="F7" t="n">
-        <v>293.0985075382</v>
+        <v>375.3123240708977</v>
       </c>
       <c r="G7" t="n">
-        <v>199.595107021608</v>
+        <v>255.6250837336162</v>
       </c>
       <c r="H7" t="n">
-        <v>6.874168604799819</v>
+        <v>156.8627780229932</v>
       </c>
       <c r="I7" t="n">
-        <v>-106.1869554804285</v>
+        <v>-36.98381447245407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0135650336873643</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0528511087280152</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.1946919093204228</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04542173664502831</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02158913630015125</v>
+        <v>0.03168885381359306</v>
       </c>
     </row>
   </sheetData>
@@ -2328,101 +2328,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pore_system.alpha_soft</t>
+          <t>pore_system.soft_pore_fraction</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.825454003329264</v>
       </c>
       <c r="C2" t="n">
-        <v>532.7939489924975</v>
+        <v>240.467230133743</v>
       </c>
       <c r="D2" t="n">
-        <v>942.9092046664233</v>
+        <v>651.3254750882118</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1098.223309906758</v>
+        <v>648.1030838384743</v>
       </c>
       <c r="G2" t="n">
-        <v>1292.83086111294</v>
+        <v>810.1582776946045</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pore_system.soft_pore_fraction</t>
+          <t>pore_system.alpha_soft</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8355537208427058</v>
+        <v>0.6339876173128379</v>
       </c>
       <c r="C3" t="n">
-        <v>240.1665724900756</v>
+        <v>241.6291795739236</v>
       </c>
       <c r="D3" t="n">
-        <v>446.0357750815936</v>
+        <v>420.4375385013089</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>658.1721100885243</v>
+        <v>850.1129952348308</v>
       </c>
       <c r="G3" t="n">
-        <v>672.3860756785596</v>
+        <v>880.2093727732636</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pore_system.alpha_hard</t>
+          <t>kerogen.G</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7020105699546</v>
+        <v>0.1783815003860008</v>
       </c>
       <c r="C4" t="n">
-        <v>22.26525691748651</v>
+        <v>26.64814043861583</v>
       </c>
       <c r="D4" t="n">
-        <v>112.9403073212518</v>
+        <v>70.20181950122139</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>200.7237779117272</v>
+        <v>141.3137568237904</v>
       </c>
       <c r="G4" t="n">
-        <v>190.6837393041581</v>
+        <v>171.5713569216706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kerogen.G</t>
+          <t>pore_system.alpha_hard</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4432205339965755</v>
+        <v>0.1043877835439755</v>
       </c>
       <c r="C5" t="n">
-        <v>18.05655223221424</v>
+        <v>22.3428102387129</v>
       </c>
       <c r="D5" t="n">
-        <v>70.32867726916879</v>
+        <v>62.75323653961408</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>153.0163740558294</v>
+        <v>133.1060147112997</v>
       </c>
       <c r="G5" t="n">
-        <v>173.3813657744907</v>
+        <v>134.5738990203222</v>
       </c>
     </row>
     <row r="6">
@@ -2432,22 +2432,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2698832062139853</v>
+        <v>0.03218021933571324</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5711473722294</v>
+        <v>50.18104326698966</v>
       </c>
       <c r="D6" t="n">
-        <v>9.479407745177923</v>
+        <v>8.878477163778427</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>110.1958333447091</v>
+        <v>125.1680938800354</v>
       </c>
       <c r="G6" t="n">
-        <v>17.576173960643</v>
+        <v>17.16079949501687</v>
       </c>
     </row>
     <row r="7">
@@ -2604,49 +2604,49 @@
         <v>0.005</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H2" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I2" t="n">
-        <v>406.45611745763</v>
+        <v>372.9267458670756</v>
       </c>
       <c r="J2" t="n">
-        <v>433.9540137393665</v>
+        <v>323.3346791527306</v>
       </c>
       <c r="K2" t="n">
-        <v>-269.9537487347862</v>
+        <v>49.17409931443349</v>
       </c>
       <c r="L2" t="n">
-        <v>-392.738921329813</v>
+        <v>-156.7931277192747</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N2" t="n">
-        <v>0.192102039516394</v>
+        <v>0.05613163066302089</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2411707179477246</v>
+        <v>0.1030936935033055</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3198974938957868</v>
+        <v>0.02852588847244666</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3011509708163725</v>
+        <v>0.1657391783899537</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2125134256629138</v>
+        <v>0.07324510217072189</v>
       </c>
     </row>
     <row r="3">
@@ -2667,49 +2667,49 @@
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G3" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H3" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I3" t="n">
-        <v>301.5137188271684</v>
+        <v>448.2121861099564</v>
       </c>
       <c r="J3" t="n">
-        <v>165.6559397097141</v>
+        <v>255.679653232361</v>
       </c>
       <c r="K3" t="n">
-        <v>88.8435757561345</v>
+        <v>305.7040850058726</v>
       </c>
       <c r="L3" t="n">
-        <v>-32.83027150092159</v>
+        <v>98.15020061719871</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01426087981848968</v>
+        <v>0.3092761004164361</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002774472024319741</v>
+        <v>0.01203839332131042</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09967253220823627</v>
+        <v>0.4914890849119914</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01561351699276239</v>
+        <v>0.1028473639579174</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0213366789838025</v>
+        <v>0.1767093480493431</v>
       </c>
     </row>
     <row r="4">
@@ -2730,49 +2730,49 @@
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G4" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H4" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I4" t="n">
-        <v>446.0316965677709</v>
+        <v>568.1626243656696</v>
       </c>
       <c r="J4" t="n">
-        <v>235.2372812467743</v>
+        <v>326.3661431214435</v>
       </c>
       <c r="K4" t="n">
-        <v>351.1046733904576</v>
+        <v>481.8089982948309</v>
       </c>
       <c r="L4" t="n">
-        <v>182.8013471247607</v>
+        <v>247.893826381756</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2591689922115333</v>
+        <v>0.7126049511340705</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06460097103569963</v>
+        <v>0.1071736692021832</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4185747740246678</v>
+        <v>0.8093080460958568</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1345947059727377</v>
+        <v>0.2634404446472925</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1715299152131245</v>
+        <v>0.3874722473450938</v>
       </c>
     </row>
     <row r="5">
@@ -2793,49 +2793,49 @@
         <v>0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G5" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H5" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I5" t="n">
-        <v>580.8035062304677</v>
+        <v>653.6342240358964</v>
       </c>
       <c r="J5" t="n">
-        <v>331.6015758274034</v>
+        <v>384.9510765508089</v>
       </c>
       <c r="K5" t="n">
-        <v>515.4484951116686</v>
+        <v>587.4722660938951</v>
       </c>
       <c r="L5" t="n">
-        <v>299.8502323262397</v>
+        <v>328.3495283123111</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4875607122197518</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1502254621997328</v>
+        <v>0.1860217462959939</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6184123162614892</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2274567160111512</v>
+        <v>0.3497254465369164</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3030630544445157</v>
+        <v>0.5316812770184149</v>
       </c>
     </row>
     <row r="6">
@@ -2856,49 +2856,49 @@
         <v>0.005</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G6" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H6" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I6" t="n">
-        <v>597.8258524054362</v>
+        <v>410.1776669657629</v>
       </c>
       <c r="J6" t="n">
-        <v>722.1495910198297</v>
+        <v>499.7245041447799</v>
       </c>
       <c r="K6" t="n">
-        <v>-509.8463798496476</v>
+        <v>-175.5902659730185</v>
       </c>
       <c r="L6" t="n">
-        <v>-692.0417597750934</v>
+        <v>-400.9321764933329</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5164077161384983</v>
+        <v>0.1813864560174522</v>
       </c>
       <c r="O6" t="n">
-        <v>0.497246889809464</v>
+        <v>0.3404925895233114</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6116002990309979</v>
+        <v>0.25667088462229</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5386061429898541</v>
+        <v>0.4275669641071573</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4539308077023966</v>
+        <v>0.2468565628301392</v>
       </c>
     </row>
     <row r="7">
@@ -2919,49 +2919,49 @@
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G7" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H7" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I7" t="n">
-        <v>319.9113146001604</v>
+        <v>375.3123240708977</v>
       </c>
       <c r="J7" t="n">
-        <v>285.427424694309</v>
+        <v>255.6250837336162</v>
       </c>
       <c r="K7" t="n">
-        <v>-112.2234547160001</v>
+        <v>156.8627780229932</v>
       </c>
       <c r="L7" t="n">
-        <v>-222.9898610005264</v>
+        <v>-36.98381447245407</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04543845733359362</v>
+        <v>0.06415304791864959</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1091974215451694</v>
+        <v>0.01196494952284323</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1281018184460827</v>
+        <v>0.2228731293257397</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1664787018991946</v>
+        <v>0.03724925695692193</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08626461115754333</v>
+        <v>0.05890834016652104</v>
       </c>
     </row>
     <row r="8">
@@ -2982,49 +2982,49 @@
         <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G8" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H8" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I8" t="n">
-        <v>360.0466693094172</v>
+        <v>506.7075415392306</v>
       </c>
       <c r="J8" t="n">
-        <v>176.0216217761862</v>
+        <v>287.0021185646766</v>
       </c>
       <c r="K8" t="n">
-        <v>223.8060310319925</v>
+        <v>400.5021493695655</v>
       </c>
       <c r="L8" t="n">
-        <v>83.20460779280856</v>
+        <v>183.1157426477831</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1134540365421016</v>
+        <v>0.5059645395808925</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01198489852484469</v>
+        <v>0.05419455902333876</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2637831453977397</v>
+        <v>0.6625724566114178</v>
       </c>
       <c r="R8" t="n">
-        <v>0.05557854625693274</v>
+        <v>0.1939689598019238</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08146279454122356</v>
+        <v>0.2824085162316863</v>
       </c>
     </row>
     <row r="9">
@@ -3045,49 +3045,49 @@
         <v>0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G9" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H9" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I9" t="n">
-        <v>525.9146770056466</v>
+        <v>624.7247514892789</v>
       </c>
       <c r="J9" t="n">
-        <v>293.3624613112176</v>
+        <v>365.5557528326195</v>
       </c>
       <c r="K9" t="n">
-        <v>450.9324984764996</v>
+        <v>553.0208924473035</v>
       </c>
       <c r="L9" t="n">
-        <v>255.5984434568114</v>
+        <v>303.2394039280899</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3945430837760185</v>
+        <v>0.9027929826131762</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1162480981017469</v>
+        <v>0.1599180385630998</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.539962648561768</v>
+        <v>0.9378251317397885</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1923490765395138</v>
+        <v>0.3227960048944666</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2505562984081161</v>
+        <v>0.4837204541409724</v>
       </c>
     </row>
     <row r="10">
@@ -3108,49 +3108,49 @@
         <v>0.005</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G10" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H10" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I10" t="n">
-        <v>735.7014424597326</v>
+        <v>498.8078606575803</v>
       </c>
       <c r="J10" t="n">
-        <v>956.3705335418709</v>
+        <v>680.4702797183257</v>
       </c>
       <c r="K10" t="n">
-        <v>-667.7008472606325</v>
+        <v>-330.0832267480137</v>
       </c>
       <c r="L10" t="n">
-        <v>-934.2607734425433</v>
+        <v>-601.8273329114716</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7500592730810086</v>
+        <v>0.4794021588396087</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7053639015168423</v>
+        <v>0.5837540564666207</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8035469658915644</v>
+        <v>0.5354864576049843</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7307732400105877</v>
+        <v>0.6430176846305743</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6350237935854077</v>
+        <v>0.4721166532640025</v>
       </c>
     </row>
     <row r="11">
@@ -3171,49 +3171,49 @@
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G11" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H11" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I11" t="n">
-        <v>410.9851718734188</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="J11" t="n">
-        <v>439.0509350867008</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="K11" t="n">
-        <v>-275.4140241449446</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="L11" t="n">
-        <v>-396.4941717195655</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1997772241905605</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2456995872635628</v>
+        <v>0.093055688451175</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3265370377890353</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3041302396815966</v>
+        <v>0.1711234448015596</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2173744143398398</v>
+        <v>0.05103354595770136</v>
       </c>
     </row>
     <row r="12">
@@ -3234,49 +3234,49 @@
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G12" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H12" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I12" t="n">
-        <v>307.8828599571352</v>
+        <v>457.4514059189218</v>
       </c>
       <c r="J12" t="n">
-        <v>162.5334681385245</v>
+        <v>260.0327412170168</v>
       </c>
       <c r="K12" t="n">
-        <v>109.6125035711014</v>
+        <v>326.5729432979623</v>
       </c>
       <c r="L12" t="n">
-        <v>-13.15005181451591</v>
+        <v>120.2810102179581</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02505437662831132</v>
+        <v>0.3403426305706109</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.01789711154319099</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1249269740604989</v>
+        <v>0.5291514007418877</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.1265816289310657</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02500510390244594</v>
+        <v>0.196030359128651</v>
       </c>
     </row>
     <row r="13">
@@ -3297,49 +3297,49 @@
         <v>0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G13" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H13" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I13" t="n">
-        <v>476.0154790502056</v>
+        <v>597.8623175176947</v>
       </c>
       <c r="J13" t="n">
-        <v>257.4447936069642</v>
+        <v>347.2891781067157</v>
       </c>
       <c r="K13" t="n">
-        <v>389.6297584387191</v>
+        <v>520.0297684868171</v>
       </c>
       <c r="L13" t="n">
-        <v>211.6706718439786</v>
+        <v>278.382039861792</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3099811588705301</v>
+        <v>0.812469055674782</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08433345550139792</v>
+        <v>0.1353334874179758</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4654202120209259</v>
+        <v>0.8782855961891508</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1574984996933153</v>
+        <v>0.2961376369483033</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2016497057797282</v>
+        <v>0.4385754741889957</v>
       </c>
     </row>
     <row r="14">
@@ -3360,49 +3360,49 @@
         <v>0.005</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G14" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H14" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I14" t="n">
-        <v>825.8924565306975</v>
+        <v>583.7834160922793</v>
       </c>
       <c r="J14" t="n">
-        <v>1142.504311688031</v>
+        <v>846.8494758454993</v>
       </c>
       <c r="K14" t="n">
-        <v>-766.9016605469527</v>
+        <v>-450.3972225089123</v>
       </c>
       <c r="L14" t="n">
-        <v>-1124.758884951912</v>
+        <v>-781.2791467745443</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9029019252981705</v>
+        <v>0.7651292775643072</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8707530647080783</v>
+        <v>0.807679883724896</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9241724114203965</v>
+        <v>0.7526187819363707</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8819069950466268</v>
+        <v>0.8354714166437085</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7647699123542173</v>
+        <v>0.6762440744512122</v>
       </c>
     </row>
     <row r="15">
@@ -3423,49 +3423,49 @@
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G15" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H15" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I15" t="n">
-        <v>510.9146926707245</v>
+        <v>372.0503779934263</v>
       </c>
       <c r="J15" t="n">
-        <v>587.5578967994219</v>
+        <v>401.2575169234997</v>
       </c>
       <c r="K15" t="n">
-        <v>-407.150008313764</v>
+        <v>-76.02340726139353</v>
       </c>
       <c r="L15" t="n">
-        <v>-553.5693433766803</v>
+        <v>-281.07601049064</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3691232854448737</v>
+        <v>0.05318487655003206</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3776554438005378</v>
+        <v>0.2079681989480522</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4867243513413764</v>
+        <v>0.07698120411833653</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4287475407528605</v>
+        <v>0.2990267952704989</v>
       </c>
       <c r="S15" t="n">
-        <v>0.34414705008358</v>
+        <v>0.1283305929121434</v>
       </c>
     </row>
     <row r="16">
@@ -3486,49 +3486,49 @@
         <v>0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G16" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H16" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I16" t="n">
-        <v>293.0985075382</v>
+        <v>417.5568942360732</v>
       </c>
       <c r="J16" t="n">
-        <v>199.595107021608</v>
+        <v>246.7350029971196</v>
       </c>
       <c r="K16" t="n">
-        <v>6.874168604799819</v>
+        <v>256.8143796682389</v>
       </c>
       <c r="L16" t="n">
-        <v>-106.1869554804285</v>
+        <v>58.26429779113551</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.2061988310066424</v>
       </c>
       <c r="O16" t="n">
-        <v>0.03293111815822988</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.4032571606981754</v>
       </c>
       <c r="R16" t="n">
-        <v>0.07381184252456013</v>
+        <v>0.06007158650355159</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01995343983443141</v>
+        <v>0.1251037727450017</v>
       </c>
     </row>
     <row r="17">
@@ -3549,49 +3549,49 @@
         <v>0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G17" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H17" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I17" t="n">
-        <v>431.4406503308625</v>
+        <v>572.1626819896273</v>
       </c>
       <c r="J17" t="n">
-        <v>224.8254492057673</v>
+        <v>329.9019181451412</v>
       </c>
       <c r="K17" t="n">
-        <v>331.3216493598058</v>
+        <v>487.688972470926</v>
       </c>
       <c r="L17" t="n">
-        <v>168.0719761610279</v>
+        <v>253.4772635073887</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2344422028695532</v>
+        <v>0.7260549948999453</v>
       </c>
       <c r="O17" t="n">
-        <v>0.05534953797663577</v>
+        <v>0.1119323852292488</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3945191639086765</v>
+        <v>0.8199197164322101</v>
       </c>
       <c r="R17" t="n">
-        <v>0.122908998826196</v>
+        <v>0.2694284215261923</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1567159492038929</v>
+        <v>0.3950461283166843</v>
       </c>
     </row>
     <row r="18">
@@ -3612,34 +3612,34 @@
         <v>0.005</v>
       </c>
       <c r="E18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G18" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H18" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I18" t="n">
-        <v>883.1891187821066</v>
+        <v>650.8046862205506</v>
       </c>
       <c r="J18" t="n">
-        <v>1287.962574584499</v>
+        <v>989.7453031679541</v>
       </c>
       <c r="K18" t="n">
-        <v>-829.2612930743965</v>
+        <v>-540.4622464162909</v>
       </c>
       <c r="L18" t="n">
-        <v>-1273.610439792984</v>
+        <v>-934.6923978804948</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0.9904857851982782</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -3648,13 +3648,13 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0.9151603703716424</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8423045629668856</v>
       </c>
     </row>
     <row r="19">
@@ -3675,49 +3675,49 @@
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G19" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H19" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I19" t="n">
-        <v>599.4709810691975</v>
+        <v>406.9438652738909</v>
       </c>
       <c r="J19" t="n">
-        <v>723.2456174649677</v>
+        <v>492.8351196507189</v>
       </c>
       <c r="K19" t="n">
-        <v>-513.2849708870756</v>
+        <v>-170.9463228578348</v>
       </c>
       <c r="L19" t="n">
-        <v>-694.5092536274956</v>
+        <v>-392.4766289754471</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5191956416408094</v>
+        <v>0.1705129190900509</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4982207640756087</v>
+        <v>0.3312203297814518</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6157815306372755</v>
+        <v>0.2482898965561428</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5405637561571822</v>
+        <v>0.4184987822871997</v>
       </c>
       <c r="S19" t="n">
-        <v>0.455882585461042</v>
+        <v>0.2386078823694783</v>
       </c>
     </row>
     <row r="20">
@@ -3738,49 +3738,49 @@
         <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G20" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H20" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I20" t="n">
-        <v>309.5800769605239</v>
+        <v>387.6941600419751</v>
       </c>
       <c r="J20" t="n">
-        <v>262.874722427049</v>
+        <v>248.5981034410221</v>
       </c>
       <c r="K20" t="n">
-        <v>-85.8089028048726</v>
+        <v>191.7510457727669</v>
       </c>
       <c r="L20" t="n">
-        <v>-195.5810225647246</v>
+        <v>-2.251067769910859</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N20" t="n">
-        <v>0.02793057389539029</v>
+        <v>0.1057865070756951</v>
       </c>
       <c r="O20" t="n">
-        <v>0.08915821859752233</v>
+        <v>0.002507502848175975</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.09598245382426457</v>
+        <v>0.2858364663880275</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1447336009049776</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.06784194853072391</v>
+        <v>0.07177492660510995</v>
       </c>
     </row>
     <row r="21">
@@ -3801,49 +3801,49 @@
         <v>0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G21" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H21" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="I21" t="n">
-        <v>392.4287063594622</v>
+        <v>547.8867574645691</v>
       </c>
       <c r="J21" t="n">
-        <v>196.9568710716968</v>
+        <v>313.6889854827446</v>
       </c>
       <c r="K21" t="n">
-        <v>275.8007050263616</v>
+        <v>456.2838493104129</v>
       </c>
       <c r="L21" t="n">
-        <v>124.9002610181847</v>
+        <v>228.6971392475557</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1683304172758738</v>
+        <v>0.6444281089862256</v>
       </c>
       <c r="O21" t="n">
-        <v>0.03058691368119928</v>
+        <v>0.09011178239417508</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3270072310470662</v>
+        <v>0.76324245835737</v>
       </c>
       <c r="R21" t="n">
-        <v>0.08865824762878453</v>
+        <v>0.2428528896834605</v>
       </c>
       <c r="S21" t="n">
-        <v>0.116214305798571</v>
+        <v>0.353596447257376</v>
       </c>
     </row>
   </sheetData>
@@ -3922,22 +3922,22 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1586480359029283</v>
+        <v>0.2501899281854278</v>
       </c>
       <c r="E2" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="F2" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="G2" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="H2" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
     </row>
     <row r="3">
@@ -3955,22 +3955,22 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.243178094909691</v>
+        <v>0.3963912092357153</v>
       </c>
       <c r="E3" t="n">
-        <v>293.0985075382</v>
+        <v>374.0950646410671</v>
       </c>
       <c r="F3" t="n">
-        <v>199.595107021608</v>
+        <v>311.7599965019389</v>
       </c>
       <c r="G3" t="n">
-        <v>6.874168604799819</v>
+        <v>89.60131466339162</v>
       </c>
       <c r="H3" t="n">
-        <v>-106.1869554804285</v>
+        <v>-153.9340513545683</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
     </row>
     <row r="4">
@@ -3991,19 +3991,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="F4" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="G4" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="H4" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
     </row>
     <row r="5">
@@ -4021,22 +4021,22 @@
         <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1551322871882571</v>
+        <v>0.324183645027453</v>
       </c>
       <c r="E5" t="n">
-        <v>293.0985075382</v>
+        <v>362.8792290807827</v>
       </c>
       <c r="F5" t="n">
-        <v>199.595107021608</v>
+        <v>274.605777555574</v>
       </c>
       <c r="G5" t="n">
-        <v>6.874168604799819</v>
+        <v>106.2205030539993</v>
       </c>
       <c r="H5" t="n">
-        <v>-106.1869554804285</v>
+        <v>-86.77059734005977</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
     </row>
     <row r="6">
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.05027051629823996</v>
       </c>
       <c r="E6" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="F6" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="G6" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="H6" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
     </row>
     <row r="7">
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02158913630015125</v>
+        <v>0.03168885381359306</v>
       </c>
       <c r="E7" t="n">
-        <v>293.0985075382</v>
+        <v>375.3123240708977</v>
       </c>
       <c r="F7" t="n">
-        <v>199.595107021608</v>
+        <v>255.6250837336162</v>
       </c>
       <c r="G7" t="n">
-        <v>6.874168604799819</v>
+        <v>156.8627780229932</v>
       </c>
       <c r="H7" t="n">
-        <v>-106.1869554804285</v>
+        <v>-36.98381447245407</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
     </row>
     <row r="8">
@@ -4118,26 +4118,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.25 | 0.02</t>
+          <t>0.2 | 0.01</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01995343983443141</v>
+        <v>0.05103354595770136</v>
       </c>
       <c r="E8" t="n">
-        <v>293.0985075382</v>
+        <v>356.2331379437711</v>
       </c>
       <c r="F8" t="n">
-        <v>199.595107021608</v>
+        <v>315.8763380058308</v>
       </c>
       <c r="G8" t="n">
-        <v>6.874168604799819</v>
+        <v>33.36777644049873</v>
       </c>
       <c r="H8" t="n">
-        <v>-106.1869554804285</v>
+        <v>-161.8136402537822</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2546476629128047</v>
+        <v>0.1970385291207984</v>
       </c>
     </row>
   </sheetData>
